--- a/tc17.xlsx
+++ b/tc17.xlsx
@@ -425,312 +425,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Attachments</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Test Case Type</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Test Step #</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Test Step Description</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Test Step Expected Result</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Test Step Attachment</t>
+          <t>"IssueID": "US_402"</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Verify Valid EDI 270 Inquiry File Generation for Delinquency Status</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>TC-EDI270-271-DEL-001</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>sample_edi270_valid_01.txt</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Generate a valid EDI 270 eligibility inquiry file with correct ISA/GS headers, 2000C subscriber loop with patient details, and ensure the file is properly formatted for the four trading partners. Verify all mandatory segments (ISA, GS, ST, BHT, HL, NM1, DMG, DTP) are present and data elements comply with the specification.</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Prepare valid subscriber and provider input data including member ID, name, DOB, gender, and trading partner ID.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Input data is prepared with correct formats and trading partner identifiers.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>sample_input_270.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Verify Valid EDI 270 Inquiry File Generation for Delinquency Status</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>TC-EDI270-271-DEL-001</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>sample_edi270_valid_01.txt</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Generate a valid EDI 270 eligibility inquiry file with correct ISA/GS headers, 2000C subscriber loop with patient details, and ensure the file is properly formatted for the four trading partners. Verify all mandatory segments (ISA, GS, ST, BHT, HL, NM1, DMG, DTP) are present and data elements comply with the specification.</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Generate the 270 file using the prepared input data.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>The 270 file is generated with correct ISA/GS headers, ST/BHT segments, and subscriber loops populated. The file contains no syntax errors.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>generated_270_01.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Verify Valid EDI 270 Inquiry File Generation for Delinquency Status</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>TC-EDI270-271-DEL-001</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>sample_edi270_valid_01.txt</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Generate a valid EDI 270 eligibility inquiry file with correct ISA/GS headers, 2000C subscriber loop with patient details, and ensure the file is properly formatted for the four trading partners. Verify all mandatory segments (ISA, GS, ST, BHT, HL, NM1, DMG, DTP) are present and data elements comply with the specification.</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Validate the generated 270 file against the ANSI X12 270 schema and implementation guide.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>The 270 file passes schema validation with no missing mandatory segments or invalid data elements.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>270_schema_validation_report.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Verify 271 Response File Includes Delinquency Status EB01=5 (Active - Pending Investigation)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>TC-EDI270-271-DEL-002</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>sample_edi271_valid_01.txt</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Receive the 271 response file corresponding to the 270 inquiry.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>271 file is received containing loop 2110C with EB segment having EB01 = "5".</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>generated_271_01.txt</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Verify 271 Response File Includes Delinquency Status EB01=5 (Active - Pending Investigation)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>TC-EDI270-271-DEL-002</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>sample_edi271_valid_01.txt</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Draft</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Validate the 271 file against the ANSI X12 271 schema and implementation guide.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>271 file passes schema validation with required segments including ISA, GS, ST, BHT, HL, NM1, REF, DTP, and EB segments correctly populated.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>271_schema_validation_report.json</t>
+          <t>"Description": "As a registered customer }</t>
         </is>
       </c>
     </row>
